--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2020_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2020_arica_y_parinacota.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:09</t>
+    <t xml:space="preserve">2026-09-24 00:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -625,7 +625,7 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="G5" s="2"/>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="2" t="n">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="G8" s="2"/>
     </row>
@@ -701,7 +701,7 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2" t="n">
-        <v>0.26</v>
+        <v>0.23</v>
       </c>
       <c r="G9" s="2"/>
     </row>
@@ -739,7 +739,7 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2" t="n">
-        <v>0.07</v>
+        <v>0.06</v>
       </c>
       <c r="G11" s="2"/>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="G12" s="2"/>
     </row>
@@ -815,7 +815,7 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="G15" s="2"/>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="2" t="n">
-        <v>-0.3</v>
+        <v>-0.29</v>
       </c>
       <c r="G17" s="2"/>
     </row>
@@ -891,7 +891,7 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" s="2" t="n">
-        <v>0.07</v>
+        <v>0.04</v>
       </c>
       <c r="G19" s="2"/>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" s="2" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="G20" s="2"/>
     </row>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" s="2" t="n">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="G39" s="2"/>
     </row>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" s="2" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="G40" s="2"/>
     </row>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" s="2" t="n">
-        <v>-0.32</v>
+        <v>-0.31</v>
       </c>
       <c r="G59" s="2"/>
     </row>
@@ -1670,7 +1670,7 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" s="2" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="G60" s="2"/>
     </row>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2020_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2020_arica_y_parinacota.xlsx
@@ -111,7 +111,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:59</t>
+    <t xml:space="preserve">2026-10-01 23:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2020_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_d_otrasrel_a_2020_arica_y_parinacota.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:07</t>
+    <t xml:space="preserve">2026-10-05 19:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
